--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ФРОЗЕН ФУУДС ЕООД/ФРОЗЕН ФУУДС ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ФРОЗЕН ФУУДС ЕООД/ФРОЗЕН ФУУДС ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="30">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,31 +55,16 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>2026-08-03</t>
-  </si>
-  <si>
-    <t>2026-08-06</t>
-  </si>
-  <si>
-    <t>2026-08-18</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>2026-08-31</t>
-  </si>
-  <si>
-    <t>1199 Varna Car Osvoboditel</t>
-  </si>
-  <si>
-    <t>1911 O5 Варна</t>
-  </si>
-  <si>
-    <t>1146 Варна Сливница</t>
-  </si>
-  <si>
-    <t>1147 Варна Ситроен</t>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>2026-09-15</t>
+  </si>
+  <si>
+    <t>Бургас</t>
+  </si>
+  <si>
+    <t>Варна Сливница</t>
   </si>
   <si>
     <t>В1835СА</t>
@@ -100,37 +82,10 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>10:35:00</t>
-  </si>
-  <si>
-    <t>16:38:00</t>
-  </si>
-  <si>
-    <t>09:55:00</t>
-  </si>
-  <si>
-    <t>10:54:00</t>
-  </si>
-  <si>
-    <t>09:14:00</t>
-  </si>
-  <si>
-    <t>3235805921 3235805921</t>
-  </si>
-  <si>
-    <t>3235939007 3235939007</t>
-  </si>
-  <si>
-    <t>3236528284 3236528284</t>
-  </si>
-  <si>
-    <t>3236943963 3236943963</t>
-  </si>
-  <si>
-    <t>3237191971 3237191971</t>
+    <t>11:44</t>
+  </si>
+  <si>
+    <t>16:14</t>
   </si>
   <si>
     <t>Общи литри по продукт / ФРОЗЕН ФУУДС ЕООД</t>
@@ -551,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -560,17 +515,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -610,301 +564,160 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
         <v>13</v>
       </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2">
+        <v>62.1</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.794</v>
+      </c>
+      <c r="H2" s="1">
+        <v>111.407</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.9</v>
+      </c>
+      <c r="J2" s="1">
+        <v>117.99</v>
+      </c>
+      <c r="K2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>145740</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3">
+        <v>35.77</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.844</v>
+      </c>
+      <c r="H3" s="1">
+        <v>65.95999999999999</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.92</v>
+      </c>
+      <c r="J3" s="1">
+        <v>68.678</v>
+      </c>
+      <c r="K3" t="s">
         <v>23</v>
       </c>
-      <c r="D2" t="s">
+      <c r="L3">
+        <v>181006</v>
+      </c>
+      <c r="M3">
+        <v>174675</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F2">
-        <v>50.21</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="D7" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="1">
-        <v>1.729</v>
-      </c>
-      <c r="I2" s="1">
-        <v>86.813</v>
-      </c>
-      <c r="J2" s="1">
-        <v>1.79</v>
-      </c>
-      <c r="K2" s="1">
-        <v>89.876</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="E7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="6">
+        <v>97.87</v>
+      </c>
+      <c r="C8" s="7">
+        <v>2</v>
+      </c>
+      <c r="D8" s="8">
+        <v>1.81227</v>
+      </c>
+      <c r="E8" s="6">
+        <v>177.37</v>
+      </c>
+      <c r="F8" s="6">
+        <v>186.67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="M2">
-        <v>426995</v>
-      </c>
-      <c r="N2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3">
-        <v>36</v>
-      </c>
-      <c r="G3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H3" s="1">
-        <v>1.737</v>
-      </c>
-      <c r="I3" s="1">
-        <v>62.532</v>
-      </c>
-      <c r="J3" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="K3" s="1">
-        <v>64.8</v>
-      </c>
-      <c r="L3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M3">
-        <v>179742</v>
-      </c>
-      <c r="N3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4">
-        <v>32.89</v>
-      </c>
-      <c r="G4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" s="1">
-        <v>1.737</v>
-      </c>
-      <c r="I4" s="1">
-        <v>57.13</v>
-      </c>
-      <c r="J4" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="K4" s="1">
-        <v>59.202</v>
-      </c>
-      <c r="L4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M4">
-        <v>180132</v>
-      </c>
-      <c r="N4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5">
-        <v>36.31</v>
-      </c>
-      <c r="G5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" s="1">
-        <v>1.779</v>
-      </c>
-      <c r="I5" s="1">
-        <v>64.595</v>
-      </c>
-      <c r="J5" s="1">
-        <v>1.85</v>
-      </c>
-      <c r="K5" s="1">
-        <v>67.17400000000001</v>
-      </c>
-      <c r="L5" t="s">
-        <v>32</v>
-      </c>
-      <c r="M5">
-        <v>180575</v>
-      </c>
-      <c r="N5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6">
-        <v>67.13</v>
-      </c>
-      <c r="G6" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" s="1">
-        <v>1.779</v>
-      </c>
-      <c r="I6" s="1">
-        <v>119.424</v>
-      </c>
-      <c r="J6" s="1">
-        <v>1.84</v>
-      </c>
-      <c r="K6" s="1">
-        <v>123.519</v>
-      </c>
-      <c r="L6" t="s">
-        <v>33</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="6">
-        <v>222.54</v>
-      </c>
-      <c r="C11" s="7">
-        <v>5</v>
-      </c>
-      <c r="D11" s="8">
-        <v>1.75471</v>
-      </c>
-      <c r="E11" s="6">
-        <v>390.49</v>
-      </c>
-      <c r="F11" s="6">
-        <v>404.57</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B12" s="10">
-        <v>222.54</v>
-      </c>
-      <c r="C12" s="11">
-        <v>5</v>
-      </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="10">
-        <v>390.49</v>
-      </c>
-      <c r="F12" s="10">
-        <v>404.57</v>
+      <c r="B9" s="10">
+        <v>97.87</v>
+      </c>
+      <c r="C9" s="11">
+        <v>2</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="E9" s="10">
+        <v>177.37</v>
+      </c>
+      <c r="F9" s="10">
+        <v>186.67</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
